--- a/artfynd/A 25548-2024 artfynd.xlsx
+++ b/artfynd/A 25548-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,6 +1030,112 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121430373</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98117</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>565526</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6626740</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist, Leif Andersson, Johan Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25548-2024 artfynd.xlsx
+++ b/artfynd/A 25548-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>121430373</v>
       </c>
       <c r="B5" t="n">
-        <v>98117</v>
+        <v>98130</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 25548-2024 artfynd.xlsx
+++ b/artfynd/A 25548-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>121430373</v>
       </c>
       <c r="B5" t="n">
-        <v>98130</v>
+        <v>98131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Leif Andersson, Johan Ennerfelt</t>
+          <t>Johan Ennerfelt, Leif Andersson, Anna-Lotta Hellqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 25548-2024 artfynd.xlsx
+++ b/artfynd/A 25548-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>121430373</v>
       </c>
       <c r="B5" t="n">
-        <v>98131</v>
+        <v>98134</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 25548-2024 artfynd.xlsx
+++ b/artfynd/A 25548-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Ennerfelt, Leif Andersson, Anna-Lotta Hellqvist</t>
+          <t>Anna-Lotta Hellqvist, Leif Andersson, Johan Ennerfelt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 25548-2024 artfynd.xlsx
+++ b/artfynd/A 25548-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>121430373</v>
       </c>
       <c r="B5" t="n">
-        <v>98134</v>
+        <v>98140</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 25548-2024 artfynd.xlsx
+++ b/artfynd/A 25548-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>121430373</v>
       </c>
       <c r="B5" t="n">
-        <v>98140</v>
+        <v>98141</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 25548-2024 artfynd.xlsx
+++ b/artfynd/A 25548-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>121430373</v>
       </c>
       <c r="B5" t="n">
-        <v>98141</v>
+        <v>98149</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 25548-2024 artfynd.xlsx
+++ b/artfynd/A 25548-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72871311</v>
+        <v>116615401</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,30 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sothällen, Vstm</t>
+          <t>Våtängen O, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565464.5110930336</v>
+        <v>565340</v>
       </c>
       <c r="R2" t="n">
-        <v>6626734.653219163</v>
+        <v>6626554</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -741,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-06-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-06-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,69 +757,79 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116615401</v>
+        <v>116615216</v>
       </c>
       <c r="B3" t="n">
-        <v>90413</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565340</v>
+        <v>565432</v>
       </c>
       <c r="R3" t="n">
-        <v>6626554</v>
+        <v>6626622</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,12 +887,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Barrblandskog, inslag av björk</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -908,66 +905,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116615216</v>
+        <v>72871311</v>
       </c>
       <c r="B4" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>223597</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Våtängen O, Vstm</t>
+          <t>Sothällen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565432</v>
+        <v>565465</v>
       </c>
       <c r="R4" t="n">
-        <v>6626622</v>
+        <v>6626735</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,12 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2018-06-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2018-06-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,39 +980,37 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrblandskog, inslag av björk</t>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430373</v>
+        <v>121430720</v>
       </c>
       <c r="B5" t="n">
-        <v>98149</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,38 +1018,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223621</v>
+        <v>223597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565526</v>
+        <v>565521</v>
       </c>
       <c r="R5" t="n">
-        <v>6626740</v>
+        <v>6626748</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1131,10 +1093,208 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
+          <t>Anna-Lotta Hellqvist, Leif Andersson, Robert Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121430372</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>565443</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6626736</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist, Leif Andersson, Robert Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121430373</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>565526</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6626740</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
           <t>Anna-Lotta Hellqvist, Leif Andersson, Johan Ennerfelt</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25548-2024 artfynd.xlsx
+++ b/artfynd/A 25548-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,64 +786,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116615216</v>
+        <v>134511784</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>99230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Våtängen O, Vstm</t>
+          <t>Långkoxet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565432</v>
+        <v>565526</v>
       </c>
       <c r="R3" t="n">
-        <v>6626622</v>
+        <v>6626735</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,12 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +883,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av björk</t>
+          <t>Väg/dikesren</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -898,17 +894,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Tom Sävström, Gunnel Sävström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>72871311</v>
+        <v>134511797</v>
       </c>
       <c r="B4" t="n">
-        <v>99038</v>
+        <v>99230</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,33 +912,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223597</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sothällen, Vstm</t>
+          <t>Långkoxet, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565465</v>
+        <v>565599</v>
       </c>
       <c r="R4" t="n">
-        <v>6626735</v>
+        <v>6626748</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,12 +978,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-06-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-06-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,71 +992,88 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Väg/dikesren</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Tom Sävström, Gunnel Sävström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430720</v>
+        <v>116615216</v>
       </c>
       <c r="B5" t="n">
-        <v>99038</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ramnäs, Vstm</t>
+          <t>Våtängen O, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565521</v>
+        <v>565432</v>
       </c>
       <c r="R5" t="n">
-        <v>6626748</v>
+        <v>6626622</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,12 +1097,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,28 +1111,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av björk</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Leif Andersson, Robert Ennerfelt</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430372</v>
+        <v>72871311</v>
       </c>
       <c r="B6" t="n">
-        <v>99155</v>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,37 +1146,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223621</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ramnäs, Vstm</t>
+          <t>Sothällen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565443</v>
+        <v>565465</v>
       </c>
       <c r="R6" t="n">
-        <v>6626736</v>
+        <v>6626735</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1165,12 +1196,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2018-06-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2018-06-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1181,26 +1212,35 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Leif Andersson, Robert Ennerfelt</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121430373</v>
+        <v>121430720</v>
       </c>
       <c r="B7" t="n">
-        <v>99155</v>
+        <v>99038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1208,38 +1248,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223621</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565526</v>
+        <v>565521</v>
       </c>
       <c r="R7" t="n">
-        <v>6626740</v>
+        <v>6626748</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1291,10 +1323,319 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
+          <t>Anna-Lotta Hellqvist, Leif Andersson, Robert Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134511836</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99115</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långkoxet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>565599</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6626748</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Dike</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Gunnel Sävström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121430372</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>565443</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6626736</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist, Leif Andersson, Robert Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121430373</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>565526</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6626740</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
           <t>Anna-Lotta Hellqvist, Leif Andersson, Johan Ennerfelt</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25548-2024 artfynd.xlsx
+++ b/artfynd/A 25548-2024 artfynd.xlsx
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tom Sävström, Gunnel Sävström</t>
+          <t>Gunnel Sävström, Tom Sävström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tom Sävström, Gunnel Sävström</t>
+          <t>Gunnel Sävström, Tom Sävström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 25548-2024 artfynd.xlsx
+++ b/artfynd/A 25548-2024 artfynd.xlsx
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunnel Sävström, Tom Sävström</t>
+          <t>Tom Sävström, Gunnel Sävström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gunnel Sävström, Tom Sävström</t>
+          <t>Tom Sävström, Gunnel Sävström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 25548-2024 artfynd.xlsx
+++ b/artfynd/A 25548-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116615401</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134511784</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134511797</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116615216</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72871311</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430720</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134511836</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430372</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1636,8 +1681,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430373</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>